--- a/shixun/李宗效工作日报.xlsx
+++ b/shixun/李宗效工作日报.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13480" windowHeight="9340"/>
+    <workbookView windowWidth="13280" windowHeight="10600"/>
   </bookViews>
   <sheets>
     <sheet name="12月" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>当日小结（12.11）</t>
+  </si>
+  <si>
+    <t>1、完成检测异物功能</t>
+  </si>
+  <si>
+    <t>2、合并检测斑点和异物代码(进度60%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.10）</t>
+  </si>
+  <si>
+    <t>1、完成检测斑点功能</t>
+  </si>
+  <si>
+    <t>2、添加检测异物功能(进度80%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.9）</t>
+  </si>
+  <si>
+    <t>1、将图中的试管分割提取出来</t>
+  </si>
+  <si>
+    <t>2、添加检测斑点功能(进度80%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.8）</t>
+  </si>
+  <si>
+    <t>1、思考代码思路，借助AI工具完成代码，错误较多</t>
+  </si>
+  <si>
+    <t>2、后续尝试先分割试管和背景</t>
+  </si>
+  <si>
+    <t>当日小结（12.7）</t>
+  </si>
+  <si>
+    <t>1、复习opencv的图像平滑，形态学转换，图像梯度，轮廓信息，直方图和模板匹配，图像特征提取，人脸检测</t>
+  </si>
+  <si>
+    <t>2、完成opencv练习</t>
+  </si>
   <si>
     <t>当日小结（12.6）</t>
   </si>
@@ -39,18 +84,6 @@
   </si>
   <si>
     <t>2、完成opencv练习的前4章</t>
-  </si>
-  <si>
-    <t>当日小结（12.7）</t>
-  </si>
-  <si>
-    <t>1、复习opencv的图像平滑，形态学转换，图像梯度，轮廓信息，直方图和模板匹配，图像特征提取，人脸检测</t>
-  </si>
-  <si>
-    <t>2、完成opencv练习</t>
-  </si>
-  <si>
-    <t>当日小结（12.8）</t>
   </si>
 </sst>
 </file>
@@ -1010,100 +1043,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:E532"/>
+  <dimension ref="B5:E545"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="73.9636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" s="1" t="s">
+    <row r="5" spans="2:2">
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="2" t="s">
+    <row r="6" spans="2:2">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="2" t="s">
+    <row r="7" spans="2:2">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="1" t="s">
+    <row r="10" spans="2:2">
+      <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="2:2">
-      <c r="B8" s="2" t="s">
+    <row r="11" spans="2:2">
+      <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="2" t="s">
+    <row r="12" spans="2:2">
+      <c r="B12" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="2"/>
-    </row>
     <row r="15" spans="2:2">
-      <c r="B15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" spans="2:2">
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="2"/>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="1"/>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="2"/>
-    </row>
     <row r="25" spans="2:2">
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="2"/>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="2:2">
+      <c r="B26" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="27" spans="2:2">
-      <c r="B27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="2"/>
@@ -1111,102 +1157,99 @@
     <row r="34" spans="2:2">
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="2"/>
-    </row>
-    <row r="55" spans="2:3">
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="2:3">
-      <c r="B56" s="2"/>
-      <c r="C56" s="3"/>
-    </row>
-    <row r="57" spans="2:3">
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58" spans="2:3">
-      <c r="B58" s="2"/>
-    </row>
-    <row r="63" spans="2:3">
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64" spans="2:3">
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" s="4"/>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" s="2"/>
-    </row>
-    <row r="68" spans="2:2">
+    <row r="38" spans="2:2">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="2"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="2"/>
+    </row>
+    <row r="68" spans="2:3">
       <c r="B68" s="2"/>
     </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="2"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="2"/>
-    </row>
-    <row r="87" spans="2:2">
-      <c r="B87" s="2"/>
-    </row>
-    <row r="88" spans="2:2">
-      <c r="B88" s="2"/>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110" s="2"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="2"/>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="2"/>
-    </row>
-    <row r="130" spans="2:2">
-      <c r="B130" s="2"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="2"/>
-    </row>
-    <row r="136" spans="2:2">
-      <c r="B136" s="2"/>
-    </row>
-    <row r="159" spans="2:2">
-      <c r="B159" s="2"/>
-    </row>
-    <row r="160" spans="2:2">
-      <c r="B160" s="2"/>
-    </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="2"/>
-    </row>
-    <row r="184" spans="2:2">
-      <c r="B184" s="2"/>
-    </row>
-    <row r="185" spans="2:2">
-      <c r="B185" s="2"/>
-    </row>
-    <row r="191" spans="2:2">
-      <c r="B191" s="2"/>
-    </row>
-    <row r="192" spans="2:2">
-      <c r="B192" s="2"/>
-    </row>
-    <row r="193" spans="2:2">
-      <c r="B193" s="5"/>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="2"/>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="2"/>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="2"/>
+    <row r="69" spans="2:3">
+      <c r="B69" s="2"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="B71" s="2"/>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="B76" s="2"/>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="B79" s="4"/>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="B80" s="2"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="2"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="2"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="2"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="2"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="2"/>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="2"/>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="2"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="2"/>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="2"/>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" s="2"/>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="2"/>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="2"/>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" s="2"/>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174" s="2"/>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="2"/>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" s="2"/>
     </row>
     <row r="204" spans="2:2">
       <c r="B204" s="2"/>
@@ -1215,255 +1258,273 @@
       <c r="B205" s="2"/>
     </row>
     <row r="206" spans="2:2">
-      <c r="B206" s="2"/>
+      <c r="B206" s="5"/>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" s="2"/>
     </row>
+    <row r="208" spans="2:2">
+      <c r="B208" s="2"/>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" s="2"/>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217" s="2"/>
+    </row>
+    <row r="218" spans="2:2">
+      <c r="B218" s="2"/>
+    </row>
     <row r="219" spans="2:2">
       <c r="B219" s="2"/>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" s="2"/>
     </row>
-    <row r="221" spans="2:2">
-      <c r="B221" s="2"/>
-    </row>
-    <row r="222" spans="2:2">
-      <c r="B222" s="2"/>
-    </row>
-    <row r="223" spans="2:2">
-      <c r="B223" s="2"/>
-    </row>
-    <row r="228" spans="2:2">
-      <c r="B228" s="2"/>
-    </row>
-    <row r="229" spans="2:2">
-      <c r="B229" s="2"/>
-    </row>
-    <row r="230" spans="2:2">
-      <c r="B230" s="2"/>
-    </row>
-    <row r="231" spans="2:2">
-      <c r="B231" s="2"/>
-    </row>
-    <row r="239" spans="2:2">
-      <c r="B239" s="2"/>
-    </row>
-    <row r="240" spans="2:2">
-      <c r="B240" s="2"/>
-    </row>
-    <row r="245" spans="2:2">
-      <c r="B245" s="2"/>
-    </row>
-    <row r="246" spans="2:2">
-      <c r="B246" s="2"/>
-    </row>
-    <row r="247" spans="2:2">
-      <c r="B247" s="2"/>
-    </row>
-    <row r="254" spans="2:2">
-      <c r="B254" s="2"/>
-    </row>
-    <row r="259" spans="2:5">
+    <row r="232" spans="2:2">
+      <c r="B232" s="2"/>
+    </row>
+    <row r="233" spans="2:2">
+      <c r="B233" s="2"/>
+    </row>
+    <row r="234" spans="2:2">
+      <c r="B234" s="2"/>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" s="2"/>
+    </row>
+    <row r="236" spans="2:2">
+      <c r="B236" s="2"/>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" s="2"/>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242" s="2"/>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="2"/>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" s="2"/>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="2"/>
+    </row>
+    <row r="253" spans="2:2">
+      <c r="B253" s="2"/>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" s="2"/>
+    </row>
+    <row r="259" spans="2:2">
       <c r="B259" s="2"/>
     </row>
-    <row r="260" spans="2:5">
+    <row r="260" spans="2:2">
       <c r="B260" s="2"/>
-      <c r="E260" s="1"/>
-    </row>
-    <row r="261" spans="2:5">
-      <c r="B261" s="2"/>
-      <c r="E261" s="1"/>
-    </row>
-    <row r="267" spans="2:5">
+    </row>
+    <row r="267" spans="2:2">
       <c r="B267" s="2"/>
     </row>
-    <row r="268" spans="2:5">
-      <c r="B268" s="2"/>
-    </row>
-    <row r="269" spans="2:5">
-      <c r="B269" s="4"/>
-    </row>
-    <row r="270" spans="2:5">
-      <c r="B270" s="2"/>
-    </row>
-    <row r="271" spans="2:5">
-      <c r="B271" s="6"/>
-    </row>
-    <row r="279" spans="2:2">
-      <c r="B279" s="2"/>
-    </row>
-    <row r="280" spans="2:2">
+    <row r="272" spans="2:2">
+      <c r="B272" s="2"/>
+    </row>
+    <row r="273" spans="2:5">
+      <c r="B273" s="2"/>
+      <c r="E273" s="1"/>
+    </row>
+    <row r="274" spans="2:5">
+      <c r="B274" s="2"/>
+      <c r="E274" s="1"/>
+    </row>
+    <row r="280" spans="2:5">
       <c r="B280" s="2"/>
     </row>
-    <row r="281" spans="2:2">
+    <row r="281" spans="2:5">
       <c r="B281" s="2"/>
     </row>
-    <row r="282" spans="2:2">
-      <c r="B282" s="2"/>
-    </row>
-    <row r="283" spans="2:2">
+    <row r="282" spans="2:5">
+      <c r="B282" s="4"/>
+    </row>
+    <row r="283" spans="2:5">
       <c r="B283" s="2"/>
     </row>
-    <row r="284" spans="2:2">
-      <c r="B284" s="2"/>
-    </row>
-    <row r="286" spans="2:2">
-      <c r="B286" s="2"/>
-    </row>
-    <row r="289" spans="2:2">
-      <c r="B289" s="2"/>
+    <row r="284" spans="2:5">
+      <c r="B284" s="6"/>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" s="2"/>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" s="2"/>
+    </row>
+    <row r="294" spans="2:2">
+      <c r="B294" s="2"/>
+    </row>
+    <row r="295" spans="2:2">
+      <c r="B295" s="2"/>
+    </row>
+    <row r="296" spans="2:2">
+      <c r="B296" s="2"/>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297" s="2"/>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" s="2"/>
     </row>
-    <row r="300" spans="2:2">
-      <c r="B300" s="2"/>
-    </row>
-    <row r="301" spans="2:2">
-      <c r="B301" s="4"/>
-    </row>
     <row r="302" spans="2:2">
       <c r="B302" s="2"/>
     </row>
-    <row r="303" spans="2:2">
-      <c r="B303" s="2"/>
-    </row>
-    <row r="309" spans="2:2">
-      <c r="B309" s="2"/>
-    </row>
-    <row r="310" spans="2:2">
-      <c r="B310" s="2"/>
-    </row>
-    <row r="328" spans="2:2">
-      <c r="B328" s="2"/>
-    </row>
-    <row r="329" spans="2:2">
-      <c r="B329" s="2"/>
-    </row>
-    <row r="338" spans="2:2">
-      <c r="B338" s="2"/>
-    </row>
-    <row r="339" spans="2:2">
-      <c r="B339" s="2"/>
-    </row>
-    <row r="340" spans="2:2">
-      <c r="B340" s="2"/>
+    <row r="312" spans="2:2">
+      <c r="B312" s="2"/>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" s="2"/>
+    </row>
+    <row r="314" spans="2:2">
+      <c r="B314" s="4"/>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" s="2"/>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" s="2"/>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322" s="2"/>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" s="2"/>
     </row>
     <row r="341" spans="2:2">
       <c r="B341" s="2"/>
     </row>
+    <row r="342" spans="2:2">
+      <c r="B342" s="2"/>
+    </row>
+    <row r="351" spans="2:2">
+      <c r="B351" s="2"/>
+    </row>
+    <row r="352" spans="2:2">
+      <c r="B352" s="2"/>
+    </row>
+    <row r="353" spans="2:2">
+      <c r="B353" s="2"/>
+    </row>
     <row r="354" spans="2:2">
       <c r="B354" s="2"/>
     </row>
-    <row r="355" spans="2:2">
-      <c r="B355" s="2"/>
-    </row>
-    <row r="356" spans="2:2">
-      <c r="B356" s="2"/>
-    </row>
-    <row r="357" spans="2:2">
-      <c r="B357" s="2"/>
-    </row>
-    <row r="362" spans="2:2">
-      <c r="B362" s="7"/>
-    </row>
-    <row r="392" spans="2:2">
-      <c r="B392" s="2"/>
-    </row>
-    <row r="393" spans="2:2">
-      <c r="B393" s="2"/>
-    </row>
-    <row r="394" spans="2:2">
-      <c r="B394" s="2"/>
-    </row>
-    <row r="395" spans="2:2">
-      <c r="B395" s="2"/>
-    </row>
-    <row r="420" spans="2:2">
-      <c r="B420" s="4"/>
-    </row>
-    <row r="421" spans="2:2">
-      <c r="B421" s="2"/>
-    </row>
-    <row r="422" spans="2:2">
-      <c r="B422" s="2"/>
-    </row>
-    <row r="423" spans="2:2">
-      <c r="B423" s="2"/>
-    </row>
-    <row r="455" spans="2:2">
-      <c r="B455" s="2"/>
-    </row>
-    <row r="456" spans="2:2">
-      <c r="B456" s="2"/>
-    </row>
-    <row r="457" spans="2:2">
-      <c r="B457" s="2"/>
-    </row>
-    <row r="458" spans="2:2">
-      <c r="B458" s="2"/>
-    </row>
-    <row r="459" spans="2:2">
-      <c r="B459" s="2"/>
-    </row>
-    <row r="461" spans="2:2">
-      <c r="B461" s="2"/>
-    </row>
-    <row r="464" spans="2:2">
-      <c r="B464" s="2"/>
-    </row>
-    <row r="465" spans="2:2">
-      <c r="B465" s="2"/>
-    </row>
-    <row r="466" spans="2:2">
-      <c r="B466" s="2"/>
-    </row>
-    <row r="467" spans="2:2">
-      <c r="B467" s="2"/>
-    </row>
-    <row r="484" spans="2:2">
-      <c r="B484" s="2"/>
-    </row>
-    <row r="485" spans="2:2">
-      <c r="B485" s="2"/>
-    </row>
-    <row r="486" spans="2:2">
-      <c r="B486" s="2"/>
-    </row>
-    <row r="501" spans="2:2">
-      <c r="B501" s="4"/>
-    </row>
-    <row r="502" spans="2:2">
-      <c r="B502" s="2"/>
-    </row>
-    <row r="503" spans="2:2">
-      <c r="B503" s="2"/>
-    </row>
-    <row r="504" spans="2:2">
-      <c r="B504" s="2"/>
-    </row>
-    <row r="505" spans="2:2">
-      <c r="B505" s="2"/>
+    <row r="367" spans="2:2">
+      <c r="B367" s="2"/>
+    </row>
+    <row r="368" spans="2:2">
+      <c r="B368" s="2"/>
+    </row>
+    <row r="369" spans="2:2">
+      <c r="B369" s="2"/>
+    </row>
+    <row r="370" spans="2:2">
+      <c r="B370" s="2"/>
+    </row>
+    <row r="375" spans="2:2">
+      <c r="B375" s="7"/>
+    </row>
+    <row r="405" spans="2:2">
+      <c r="B405" s="2"/>
+    </row>
+    <row r="406" spans="2:2">
+      <c r="B406" s="2"/>
+    </row>
+    <row r="407" spans="2:2">
+      <c r="B407" s="2"/>
+    </row>
+    <row r="408" spans="2:2">
+      <c r="B408" s="2"/>
+    </row>
+    <row r="433" spans="2:2">
+      <c r="B433" s="4"/>
+    </row>
+    <row r="434" spans="2:2">
+      <c r="B434" s="2"/>
+    </row>
+    <row r="435" spans="2:2">
+      <c r="B435" s="2"/>
+    </row>
+    <row r="436" spans="2:2">
+      <c r="B436" s="2"/>
+    </row>
+    <row r="468" spans="2:2">
+      <c r="B468" s="2"/>
+    </row>
+    <row r="469" spans="2:2">
+      <c r="B469" s="2"/>
+    </row>
+    <row r="470" spans="2:2">
+      <c r="B470" s="2"/>
+    </row>
+    <row r="471" spans="2:2">
+      <c r="B471" s="2"/>
+    </row>
+    <row r="472" spans="2:2">
+      <c r="B472" s="2"/>
+    </row>
+    <row r="474" spans="2:2">
+      <c r="B474" s="2"/>
+    </row>
+    <row r="477" spans="2:2">
+      <c r="B477" s="2"/>
+    </row>
+    <row r="478" spans="2:2">
+      <c r="B478" s="2"/>
+    </row>
+    <row r="479" spans="2:2">
+      <c r="B479" s="2"/>
+    </row>
+    <row r="480" spans="2:2">
+      <c r="B480" s="2"/>
+    </row>
+    <row r="497" spans="2:2">
+      <c r="B497" s="2"/>
+    </row>
+    <row r="498" spans="2:2">
+      <c r="B498" s="2"/>
+    </row>
+    <row r="499" spans="2:2">
+      <c r="B499" s="2"/>
     </row>
     <row r="514" spans="2:2">
-      <c r="B514" s="2"/>
-    </row>
-    <row r="520" spans="2:2">
-      <c r="B520" s="2"/>
-    </row>
-    <row r="521" spans="2:2">
-      <c r="B521" s="2"/>
-    </row>
-    <row r="523" spans="2:2">
-      <c r="B523" s="2"/>
-    </row>
-    <row r="524" spans="2:2">
-      <c r="B524" s="2"/>
-    </row>
-    <row r="532" spans="2:2">
-      <c r="B532" s="2"/>
+      <c r="B514" s="4"/>
+    </row>
+    <row r="515" spans="2:2">
+      <c r="B515" s="2"/>
+    </row>
+    <row r="516" spans="2:2">
+      <c r="B516" s="2"/>
+    </row>
+    <row r="517" spans="2:2">
+      <c r="B517" s="2"/>
+    </row>
+    <row r="518" spans="2:2">
+      <c r="B518" s="2"/>
+    </row>
+    <row r="527" spans="2:2">
+      <c r="B527" s="2"/>
+    </row>
+    <row r="533" spans="2:2">
+      <c r="B533" s="2"/>
+    </row>
+    <row r="534" spans="2:2">
+      <c r="B534" s="2"/>
+    </row>
+    <row r="536" spans="2:2">
+      <c r="B536" s="2"/>
+    </row>
+    <row r="537" spans="2:2">
+      <c r="B537" s="2"/>
+    </row>
+    <row r="545" spans="2:2">
+      <c r="B545" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/shixun/李宗效工作日报.xlsx
+++ b/shixun/李宗效工作日报.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13280" windowHeight="10600"/>
+    <workbookView windowWidth="25600" windowHeight="11190"/>
   </bookViews>
   <sheets>
     <sheet name="12月" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>当日小结（12.12）</t>
+  </si>
+  <si>
+    <t>1、完成合并检测斑点和异物代码</t>
+  </si>
+  <si>
+    <t>2、添加检测凹陷功能(进度50%)</t>
+  </si>
   <si>
     <t>当日小结（12.11）</t>
   </si>
@@ -1043,7 +1052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B5:E545"/>
+  <dimension ref="B5:E550"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="73.9636363636364" customWidth="1"/>
@@ -1079,9 +1088,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="2"/>
-    </row>
     <row r="15" spans="2:2">
       <c r="B15" s="1" t="s">
         <v>6</v>
@@ -1097,6 +1103,9 @@
         <v>8</v>
       </c>
     </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="2"/>
+    </row>
     <row r="20" spans="2:2">
       <c r="B20" s="1" t="s">
         <v>9</v>
@@ -1112,15 +1121,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="2"/>
-    </row>
     <row r="25" spans="2:2">
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" ht="28" spans="2:2">
+    <row r="26" spans="2:2">
       <c r="B26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1131,17 +1137,14 @@
       </c>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="1"/>
+      <c r="B28" s="2"/>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" ht="28" spans="2:2">
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
@@ -1152,10 +1155,25 @@
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="2"/>
+      <c r="B33" s="1"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="2"/>
+      <c r="B34" s="1"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="2"/>
@@ -1163,368 +1181,374 @@
     <row r="39" spans="2:2">
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="2"/>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="2"/>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="2"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="2"/>
-    </row>
-    <row r="68" spans="2:3">
-      <c r="B68" s="2"/>
-    </row>
-    <row r="69" spans="2:3">
-      <c r="B69" s="2"/>
-      <c r="C69" s="3"/>
-    </row>
-    <row r="70" spans="2:3">
-      <c r="B70" s="2"/>
-    </row>
-    <row r="71" spans="2:3">
-      <c r="B71" s="2"/>
+    <row r="43" spans="2:2">
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="2"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="2"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="2"/>
+    </row>
+    <row r="73" spans="2:3">
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="2:3">
+      <c r="B74" s="2"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3">
+      <c r="B75" s="2"/>
     </row>
     <row r="76" spans="2:3">
       <c r="B76" s="2"/>
     </row>
-    <row r="77" spans="2:3">
-      <c r="B77" s="2"/>
-    </row>
-    <row r="78" spans="2:3">
-      <c r="B78" s="2"/>
-    </row>
-    <row r="79" spans="2:3">
-      <c r="B79" s="4"/>
-    </row>
-    <row r="80" spans="2:3">
-      <c r="B80" s="2"/>
-    </row>
     <row r="81" spans="2:2">
       <c r="B81" s="2"/>
     </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="2"/>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="2"/>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="2"/>
+    <row r="82" spans="2:2">
+      <c r="B82" s="2"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="2"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="4"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="2"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="2"/>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" s="2"/>
     </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="2"/>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="2"/>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125" s="2"/>
-    </row>
-    <row r="143" spans="2:2">
-      <c r="B143" s="2"/>
+    <row r="102" spans="2:2">
+      <c r="B102" s="2"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="2"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="2"/>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="2"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="2"/>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="2"/>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" s="2"/>
     </row>
-    <row r="149" spans="2:2">
-      <c r="B149" s="2"/>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="2"/>
-    </row>
-    <row r="173" spans="2:2">
-      <c r="B173" s="2"/>
-    </row>
-    <row r="174" spans="2:2">
-      <c r="B174" s="2"/>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="2"/>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" s="2"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="2"/>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="2"/>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="5"/>
-    </row>
-    <row r="207" spans="2:2">
-      <c r="B207" s="2"/>
-    </row>
-    <row r="208" spans="2:2">
-      <c r="B208" s="2"/>
-    </row>
-    <row r="216" spans="2:2">
-      <c r="B216" s="2"/>
-    </row>
-    <row r="217" spans="2:2">
-      <c r="B217" s="2"/>
-    </row>
-    <row r="218" spans="2:2">
-      <c r="B218" s="2"/>
-    </row>
-    <row r="219" spans="2:2">
-      <c r="B219" s="2"/>
-    </row>
-    <row r="220" spans="2:2">
-      <c r="B220" s="2"/>
-    </row>
-    <row r="232" spans="2:2">
-      <c r="B232" s="2"/>
-    </row>
-    <row r="233" spans="2:2">
-      <c r="B233" s="2"/>
-    </row>
-    <row r="234" spans="2:2">
-      <c r="B234" s="2"/>
-    </row>
-    <row r="235" spans="2:2">
-      <c r="B235" s="2"/>
-    </row>
-    <row r="236" spans="2:2">
-      <c r="B236" s="2"/>
+    <row r="153" spans="2:2">
+      <c r="B153" s="2"/>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="2"/>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="2"/>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="2"/>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="2"/>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202" s="2"/>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="2"/>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" s="2"/>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="2"/>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="2"/>
+    </row>
+    <row r="213" spans="2:2">
+      <c r="B213" s="2"/>
+    </row>
+    <row r="221" spans="2:2">
+      <c r="B221" s="2"/>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222" s="2"/>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" s="2"/>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="2"/>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" s="2"/>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" s="2"/>
+    </row>
+    <row r="238" spans="2:2">
+      <c r="B238" s="2"/>
+    </row>
+    <row r="239" spans="2:2">
+      <c r="B239" s="2"/>
+    </row>
+    <row r="240" spans="2:2">
+      <c r="B240" s="2"/>
     </row>
     <row r="241" spans="2:2">
       <c r="B241" s="2"/>
     </row>
-    <row r="242" spans="2:2">
-      <c r="B242" s="2"/>
-    </row>
-    <row r="243" spans="2:2">
-      <c r="B243" s="2"/>
-    </row>
-    <row r="244" spans="2:2">
-      <c r="B244" s="2"/>
-    </row>
-    <row r="252" spans="2:2">
-      <c r="B252" s="2"/>
-    </row>
-    <row r="253" spans="2:2">
-      <c r="B253" s="2"/>
+    <row r="246" spans="2:2">
+      <c r="B246" s="2"/>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247" s="2"/>
+    </row>
+    <row r="248" spans="2:2">
+      <c r="B248" s="2"/>
+    </row>
+    <row r="249" spans="2:2">
+      <c r="B249" s="2"/>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257" s="2"/>
     </row>
     <row r="258" spans="2:2">
       <c r="B258" s="2"/>
     </row>
-    <row r="259" spans="2:2">
-      <c r="B259" s="2"/>
-    </row>
-    <row r="260" spans="2:2">
-      <c r="B260" s="2"/>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" s="2"/>
+    <row r="263" spans="2:2">
+      <c r="B263" s="2"/>
+    </row>
+    <row r="264" spans="2:2">
+      <c r="B264" s="2"/>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" s="2"/>
     </row>
     <row r="272" spans="2:2">
       <c r="B272" s="2"/>
     </row>
-    <row r="273" spans="2:5">
-      <c r="B273" s="2"/>
-      <c r="E273" s="1"/>
-    </row>
-    <row r="274" spans="2:5">
-      <c r="B274" s="2"/>
-      <c r="E274" s="1"/>
-    </row>
-    <row r="280" spans="2:5">
-      <c r="B280" s="2"/>
-    </row>
-    <row r="281" spans="2:5">
-      <c r="B281" s="2"/>
-    </row>
-    <row r="282" spans="2:5">
-      <c r="B282" s="4"/>
-    </row>
-    <row r="283" spans="2:5">
-      <c r="B283" s="2"/>
-    </row>
-    <row r="284" spans="2:5">
-      <c r="B284" s="6"/>
-    </row>
-    <row r="292" spans="2:2">
-      <c r="B292" s="2"/>
-    </row>
-    <row r="293" spans="2:2">
-      <c r="B293" s="2"/>
-    </row>
-    <row r="294" spans="2:2">
-      <c r="B294" s="2"/>
-    </row>
-    <row r="295" spans="2:2">
-      <c r="B295" s="2"/>
-    </row>
-    <row r="296" spans="2:2">
-      <c r="B296" s="2"/>
+    <row r="277" spans="2:5">
+      <c r="B277" s="2"/>
+    </row>
+    <row r="278" spans="2:5">
+      <c r="B278" s="2"/>
+      <c r="E278" s="1"/>
+    </row>
+    <row r="279" spans="2:5">
+      <c r="B279" s="2"/>
+      <c r="E279" s="1"/>
+    </row>
+    <row r="285" spans="2:5">
+      <c r="B285" s="2"/>
+    </row>
+    <row r="286" spans="2:5">
+      <c r="B286" s="2"/>
+    </row>
+    <row r="287" spans="2:5">
+      <c r="B287" s="4"/>
+    </row>
+    <row r="288" spans="2:5">
+      <c r="B288" s="2"/>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" s="6"/>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" s="2"/>
     </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="2"/>
+    </row>
     <row r="299" spans="2:2">
       <c r="B299" s="2"/>
     </row>
+    <row r="300" spans="2:2">
+      <c r="B300" s="2"/>
+    </row>
+    <row r="301" spans="2:2">
+      <c r="B301" s="2"/>
+    </row>
     <row r="302" spans="2:2">
       <c r="B302" s="2"/>
     </row>
-    <row r="312" spans="2:2">
-      <c r="B312" s="2"/>
-    </row>
-    <row r="313" spans="2:2">
-      <c r="B313" s="2"/>
-    </row>
-    <row r="314" spans="2:2">
-      <c r="B314" s="4"/>
-    </row>
-    <row r="315" spans="2:2">
-      <c r="B315" s="2"/>
-    </row>
-    <row r="316" spans="2:2">
-      <c r="B316" s="2"/>
-    </row>
-    <row r="322" spans="2:2">
-      <c r="B322" s="2"/>
-    </row>
-    <row r="323" spans="2:2">
-      <c r="B323" s="2"/>
-    </row>
-    <row r="341" spans="2:2">
-      <c r="B341" s="2"/>
-    </row>
-    <row r="342" spans="2:2">
-      <c r="B342" s="2"/>
-    </row>
-    <row r="351" spans="2:2">
-      <c r="B351" s="2"/>
-    </row>
-    <row r="352" spans="2:2">
-      <c r="B352" s="2"/>
-    </row>
-    <row r="353" spans="2:2">
-      <c r="B353" s="2"/>
-    </row>
-    <row r="354" spans="2:2">
-      <c r="B354" s="2"/>
-    </row>
-    <row r="367" spans="2:2">
-      <c r="B367" s="2"/>
-    </row>
-    <row r="368" spans="2:2">
-      <c r="B368" s="2"/>
-    </row>
-    <row r="369" spans="2:2">
-      <c r="B369" s="2"/>
-    </row>
-    <row r="370" spans="2:2">
-      <c r="B370" s="2"/>
+    <row r="304" spans="2:2">
+      <c r="B304" s="2"/>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307" s="2"/>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317" s="2"/>
+    </row>
+    <row r="318" spans="2:2">
+      <c r="B318" s="2"/>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" s="4"/>
+    </row>
+    <row r="320" spans="2:2">
+      <c r="B320" s="2"/>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" s="2"/>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327" s="2"/>
+    </row>
+    <row r="328" spans="2:2">
+      <c r="B328" s="2"/>
+    </row>
+    <row r="346" spans="2:2">
+      <c r="B346" s="2"/>
+    </row>
+    <row r="347" spans="2:2">
+      <c r="B347" s="2"/>
+    </row>
+    <row r="356" spans="2:2">
+      <c r="B356" s="2"/>
+    </row>
+    <row r="357" spans="2:2">
+      <c r="B357" s="2"/>
+    </row>
+    <row r="358" spans="2:2">
+      <c r="B358" s="2"/>
+    </row>
+    <row r="359" spans="2:2">
+      <c r="B359" s="2"/>
+    </row>
+    <row r="372" spans="2:2">
+      <c r="B372" s="2"/>
+    </row>
+    <row r="373" spans="2:2">
+      <c r="B373" s="2"/>
+    </row>
+    <row r="374" spans="2:2">
+      <c r="B374" s="2"/>
     </row>
     <row r="375" spans="2:2">
-      <c r="B375" s="7"/>
-    </row>
-    <row r="405" spans="2:2">
-      <c r="B405" s="2"/>
-    </row>
-    <row r="406" spans="2:2">
-      <c r="B406" s="2"/>
-    </row>
-    <row r="407" spans="2:2">
-      <c r="B407" s="2"/>
-    </row>
-    <row r="408" spans="2:2">
-      <c r="B408" s="2"/>
-    </row>
-    <row r="433" spans="2:2">
-      <c r="B433" s="4"/>
-    </row>
-    <row r="434" spans="2:2">
-      <c r="B434" s="2"/>
-    </row>
-    <row r="435" spans="2:2">
-      <c r="B435" s="2"/>
-    </row>
-    <row r="436" spans="2:2">
-      <c r="B436" s="2"/>
-    </row>
-    <row r="468" spans="2:2">
-      <c r="B468" s="2"/>
-    </row>
-    <row r="469" spans="2:2">
-      <c r="B469" s="2"/>
-    </row>
-    <row r="470" spans="2:2">
-      <c r="B470" s="2"/>
-    </row>
-    <row r="471" spans="2:2">
-      <c r="B471" s="2"/>
-    </row>
-    <row r="472" spans="2:2">
-      <c r="B472" s="2"/>
+      <c r="B375" s="2"/>
+    </row>
+    <row r="380" spans="2:2">
+      <c r="B380" s="7"/>
+    </row>
+    <row r="410" spans="2:2">
+      <c r="B410" s="2"/>
+    </row>
+    <row r="411" spans="2:2">
+      <c r="B411" s="2"/>
+    </row>
+    <row r="412" spans="2:2">
+      <c r="B412" s="2"/>
+    </row>
+    <row r="413" spans="2:2">
+      <c r="B413" s="2"/>
+    </row>
+    <row r="438" spans="2:2">
+      <c r="B438" s="4"/>
+    </row>
+    <row r="439" spans="2:2">
+      <c r="B439" s="2"/>
+    </row>
+    <row r="440" spans="2:2">
+      <c r="B440" s="2"/>
+    </row>
+    <row r="441" spans="2:2">
+      <c r="B441" s="2"/>
+    </row>
+    <row r="473" spans="2:2">
+      <c r="B473" s="2"/>
     </row>
     <row r="474" spans="2:2">
       <c r="B474" s="2"/>
     </row>
+    <row r="475" spans="2:2">
+      <c r="B475" s="2"/>
+    </row>
+    <row r="476" spans="2:2">
+      <c r="B476" s="2"/>
+    </row>
     <row r="477" spans="2:2">
       <c r="B477" s="2"/>
     </row>
-    <row r="478" spans="2:2">
-      <c r="B478" s="2"/>
-    </row>
     <row r="479" spans="2:2">
       <c r="B479" s="2"/>
     </row>
-    <row r="480" spans="2:2">
-      <c r="B480" s="2"/>
-    </row>
-    <row r="497" spans="2:2">
-      <c r="B497" s="2"/>
-    </row>
-    <row r="498" spans="2:2">
-      <c r="B498" s="2"/>
-    </row>
-    <row r="499" spans="2:2">
-      <c r="B499" s="2"/>
-    </row>
-    <row r="514" spans="2:2">
-      <c r="B514" s="4"/>
-    </row>
-    <row r="515" spans="2:2">
-      <c r="B515" s="2"/>
-    </row>
-    <row r="516" spans="2:2">
-      <c r="B516" s="2"/>
-    </row>
-    <row r="517" spans="2:2">
-      <c r="B517" s="2"/>
-    </row>
-    <row r="518" spans="2:2">
-      <c r="B518" s="2"/>
-    </row>
-    <row r="527" spans="2:2">
-      <c r="B527" s="2"/>
-    </row>
-    <row r="533" spans="2:2">
-      <c r="B533" s="2"/>
-    </row>
-    <row r="534" spans="2:2">
-      <c r="B534" s="2"/>
-    </row>
-    <row r="536" spans="2:2">
-      <c r="B536" s="2"/>
-    </row>
-    <row r="537" spans="2:2">
-      <c r="B537" s="2"/>
-    </row>
-    <row r="545" spans="2:2">
-      <c r="B545" s="2"/>
+    <row r="482" spans="2:2">
+      <c r="B482" s="2"/>
+    </row>
+    <row r="483" spans="2:2">
+      <c r="B483" s="2"/>
+    </row>
+    <row r="484" spans="2:2">
+      <c r="B484" s="2"/>
+    </row>
+    <row r="485" spans="2:2">
+      <c r="B485" s="2"/>
+    </row>
+    <row r="502" spans="2:2">
+      <c r="B502" s="2"/>
+    </row>
+    <row r="503" spans="2:2">
+      <c r="B503" s="2"/>
+    </row>
+    <row r="504" spans="2:2">
+      <c r="B504" s="2"/>
+    </row>
+    <row r="519" spans="2:2">
+      <c r="B519" s="4"/>
+    </row>
+    <row r="520" spans="2:2">
+      <c r="B520" s="2"/>
+    </row>
+    <row r="521" spans="2:2">
+      <c r="B521" s="2"/>
+    </row>
+    <row r="522" spans="2:2">
+      <c r="B522" s="2"/>
+    </row>
+    <row r="523" spans="2:2">
+      <c r="B523" s="2"/>
+    </row>
+    <row r="532" spans="2:2">
+      <c r="B532" s="2"/>
+    </row>
+    <row r="538" spans="2:2">
+      <c r="B538" s="2"/>
+    </row>
+    <row r="539" spans="2:2">
+      <c r="B539" s="2"/>
+    </row>
+    <row r="541" spans="2:2">
+      <c r="B541" s="2"/>
+    </row>
+    <row r="542" spans="2:2">
+      <c r="B542" s="2"/>
+    </row>
+    <row r="550" spans="2:2">
+      <c r="B550" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/shixun/李宗效工作日报.xlsx
+++ b/shixun/李宗效工作日报.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11190"/>
+    <workbookView windowWidth="15720" windowHeight="11090"/>
   </bookViews>
   <sheets>
     <sheet name="12月" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t>当日小结（12.16）</t>
+  </si>
+  <si>
+    <t>1、复习C++(20%)</t>
+  </si>
+  <si>
+    <t>2、QT安装并运行</t>
+  </si>
+  <si>
+    <t>3、2道leetcode</t>
+  </si>
+  <si>
+    <t>当日小结（12.15）</t>
+  </si>
+  <si>
+    <t>1、完成检测黑点功能</t>
+  </si>
+  <si>
+    <t>2、完成整合检测代码</t>
+  </si>
+  <si>
+    <t>3、完成汇报PPT</t>
+  </si>
+  <si>
+    <t>当日小结（12.14）</t>
+  </si>
+  <si>
+    <t>1、完成整合斑点，异物，凹陷代码</t>
+  </si>
+  <si>
+    <t>2、添加检测黑点功能(进度80%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.13）</t>
+  </si>
+  <si>
+    <t>1、完成检测凹陷功能</t>
+  </si>
+  <si>
+    <t>2、整合斑点，异物，凹陷代码(进度80%)</t>
+  </si>
   <si>
     <t>当日小结（12.12）</t>
   </si>
@@ -1052,264 +1094,313 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B5:E550"/>
+  <dimension ref="B1:E568"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="73.9636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:2">
-      <c r="B5" s="1" t="s">
+    <row r="1" spans="2:2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="2" t="s">
+    <row r="2" spans="2:2">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="7" spans="2:2">
-      <c r="B7" s="2" t="s">
-        <v>2</v>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="2" t="s">
-        <v>5</v>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="2:2">
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="2" t="s">
-        <v>8</v>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="2"/>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="2" t="s">
-        <v>11</v>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:2">
-      <c r="B25" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="2" t="s">
-        <v>14</v>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="2"/>
+      <c r="B28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" spans="2:2">
-      <c r="B30" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" ht="28" spans="2:2">
-      <c r="B31" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="2" t="s">
-        <v>17</v>
+      <c r="B30" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="1"/>
+      <c r="B34" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="1" t="s">
-        <v>18</v>
+      <c r="B35" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="B36" s="2"/>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="2"/>
+      <c r="B38" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="43" spans="2:2">
-      <c r="B43" s="2"/>
+      <c r="B43" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="44" spans="2:2">
-      <c r="B44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" ht="28" spans="2:2">
+      <c r="B49" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" s="2"/>
+      <c r="B51" s="1"/>
     </row>
     <row r="52" spans="2:2">
-      <c r="B52" s="2"/>
+      <c r="B52" s="1"/>
     </row>
     <row r="53" spans="2:2">
-      <c r="B53" s="2"/>
-    </row>
-    <row r="73" spans="2:3">
-      <c r="B73" s="2"/>
-    </row>
-    <row r="74" spans="2:3">
-      <c r="B74" s="2"/>
-      <c r="C74" s="3"/>
-    </row>
-    <row r="75" spans="2:3">
-      <c r="B75" s="2"/>
-    </row>
-    <row r="76" spans="2:3">
-      <c r="B76" s="2"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="2"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="2"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="2"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="4"/>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="2"/>
-    </row>
-    <row r="86" spans="2:2">
-      <c r="B86" s="2"/>
+      <c r="B53" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="2"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="2"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="2"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="2"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="2"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="2"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="2"/>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" s="2"/>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="B92" s="2"/>
+      <c r="C92" s="3"/>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="B93" s="2"/>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="B94" s="2"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="2"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="2"/>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" s="2"/>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="2"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="2"/>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="2"/>
-    </row>
-    <row r="128" spans="2:2">
-      <c r="B128" s="2"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="2"/>
-    </row>
-    <row r="130" spans="2:2">
-      <c r="B130" s="2"/>
+      <c r="B102" s="4"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="2"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="2"/>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="2"/>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="2"/>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="2"/>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="2"/>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" s="2"/>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="2"/>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" s="2"/>
     </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="2"/>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="2"/>
-    </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="2"/>
-    </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="2"/>
-    </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="2"/>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" s="2"/>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="209" spans="2:2">
-      <c r="B209" s="2"/>
-    </row>
-    <row r="210" spans="2:2">
-      <c r="B210" s="2"/>
-    </row>
-    <row r="211" spans="2:2">
-      <c r="B211" s="5"/>
-    </row>
-    <row r="212" spans="2:2">
-      <c r="B212" s="2"/>
-    </row>
-    <row r="213" spans="2:2">
-      <c r="B213" s="2"/>
+    <row r="166" spans="2:2">
+      <c r="B166" s="2"/>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="2"/>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="2"/>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="2"/>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="2"/>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="2"/>
+    </row>
+    <row r="220" spans="2:2">
+      <c r="B220" s="2"/>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" s="2"/>
     </row>
-    <row r="222" spans="2:2">
-      <c r="B222" s="2"/>
-    </row>
-    <row r="223" spans="2:2">
-      <c r="B223" s="2"/>
-    </row>
-    <row r="224" spans="2:2">
-      <c r="B224" s="2"/>
-    </row>
-    <row r="225" spans="2:2">
-      <c r="B225" s="2"/>
-    </row>
-    <row r="237" spans="2:2">
-      <c r="B237" s="2"/>
-    </row>
-    <row r="238" spans="2:2">
-      <c r="B238" s="2"/>
+    <row r="227" spans="2:2">
+      <c r="B227" s="2"/>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" s="2"/>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" s="5"/>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" s="2"/>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" s="2"/>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" s="2"/>
@@ -1320,17 +1411,17 @@
     <row r="241" spans="2:2">
       <c r="B241" s="2"/>
     </row>
-    <row r="246" spans="2:2">
-      <c r="B246" s="2"/>
-    </row>
-    <row r="247" spans="2:2">
-      <c r="B247" s="2"/>
-    </row>
-    <row r="248" spans="2:2">
-      <c r="B248" s="2"/>
-    </row>
-    <row r="249" spans="2:2">
-      <c r="B249" s="2"/>
+    <row r="242" spans="2:2">
+      <c r="B242" s="2"/>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="2"/>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="2"/>
+    </row>
+    <row r="256" spans="2:2">
+      <c r="B256" s="2"/>
     </row>
     <row r="257" spans="2:2">
       <c r="B257" s="2"/>
@@ -1338,8 +1429,8 @@
     <row r="258" spans="2:2">
       <c r="B258" s="2"/>
     </row>
-    <row r="263" spans="2:2">
-      <c r="B263" s="2"/>
+    <row r="259" spans="2:2">
+      <c r="B259" s="2"/>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" s="2"/>
@@ -1347,58 +1438,61 @@
     <row r="265" spans="2:2">
       <c r="B265" s="2"/>
     </row>
-    <row r="272" spans="2:2">
-      <c r="B272" s="2"/>
-    </row>
-    <row r="277" spans="2:5">
-      <c r="B277" s="2"/>
-    </row>
-    <row r="278" spans="2:5">
-      <c r="B278" s="2"/>
-      <c r="E278" s="1"/>
-    </row>
-    <row r="279" spans="2:5">
-      <c r="B279" s="2"/>
-      <c r="E279" s="1"/>
-    </row>
-    <row r="285" spans="2:5">
-      <c r="B285" s="2"/>
-    </row>
-    <row r="286" spans="2:5">
-      <c r="B286" s="2"/>
-    </row>
-    <row r="287" spans="2:5">
-      <c r="B287" s="4"/>
-    </row>
-    <row r="288" spans="2:5">
-      <c r="B288" s="2"/>
-    </row>
-    <row r="289" spans="2:2">
-      <c r="B289" s="6"/>
-    </row>
-    <row r="297" spans="2:2">
+    <row r="266" spans="2:2">
+      <c r="B266" s="2"/>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" s="2"/>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" s="2"/>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" s="2"/>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" s="2"/>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" s="2"/>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" s="2"/>
+    </row>
+    <row r="290" spans="2:5">
+      <c r="B290" s="2"/>
+    </row>
+    <row r="295" spans="2:5">
+      <c r="B295" s="2"/>
+    </row>
+    <row r="296" spans="2:5">
+      <c r="B296" s="2"/>
+      <c r="E296" s="1"/>
+    </row>
+    <row r="297" spans="2:5">
       <c r="B297" s="2"/>
-    </row>
-    <row r="298" spans="2:2">
-      <c r="B298" s="2"/>
-    </row>
-    <row r="299" spans="2:2">
-      <c r="B299" s="2"/>
-    </row>
-    <row r="300" spans="2:2">
-      <c r="B300" s="2"/>
-    </row>
-    <row r="301" spans="2:2">
-      <c r="B301" s="2"/>
-    </row>
-    <row r="302" spans="2:2">
-      <c r="B302" s="2"/>
-    </row>
-    <row r="304" spans="2:2">
+      <c r="E297" s="1"/>
+    </row>
+    <row r="303" spans="2:5">
+      <c r="B303" s="2"/>
+    </row>
+    <row r="304" spans="2:5">
       <c r="B304" s="2"/>
     </row>
+    <row r="305" spans="2:2">
+      <c r="B305" s="4"/>
+    </row>
+    <row r="306" spans="2:2">
+      <c r="B306" s="2"/>
+    </row>
     <row r="307" spans="2:2">
-      <c r="B307" s="2"/>
+      <c r="B307" s="6"/>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" s="2"/>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" s="2"/>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" s="2"/>
@@ -1407,43 +1501,43 @@
       <c r="B318" s="2"/>
     </row>
     <row r="319" spans="2:2">
-      <c r="B319" s="4"/>
+      <c r="B319" s="2"/>
     </row>
     <row r="320" spans="2:2">
       <c r="B320" s="2"/>
     </row>
-    <row r="321" spans="2:2">
-      <c r="B321" s="2"/>
-    </row>
-    <row r="327" spans="2:2">
-      <c r="B327" s="2"/>
-    </row>
-    <row r="328" spans="2:2">
-      <c r="B328" s="2"/>
+    <row r="322" spans="2:2">
+      <c r="B322" s="2"/>
+    </row>
+    <row r="325" spans="2:2">
+      <c r="B325" s="2"/>
+    </row>
+    <row r="335" spans="2:2">
+      <c r="B335" s="2"/>
+    </row>
+    <row r="336" spans="2:2">
+      <c r="B336" s="2"/>
+    </row>
+    <row r="337" spans="2:2">
+      <c r="B337" s="4"/>
+    </row>
+    <row r="338" spans="2:2">
+      <c r="B338" s="2"/>
+    </row>
+    <row r="339" spans="2:2">
+      <c r="B339" s="2"/>
+    </row>
+    <row r="345" spans="2:2">
+      <c r="B345" s="2"/>
     </row>
     <row r="346" spans="2:2">
       <c r="B346" s="2"/>
     </row>
-    <row r="347" spans="2:2">
-      <c r="B347" s="2"/>
-    </row>
-    <row r="356" spans="2:2">
-      <c r="B356" s="2"/>
-    </row>
-    <row r="357" spans="2:2">
-      <c r="B357" s="2"/>
-    </row>
-    <row r="358" spans="2:2">
-      <c r="B358" s="2"/>
-    </row>
-    <row r="359" spans="2:2">
-      <c r="B359" s="2"/>
-    </row>
-    <row r="372" spans="2:2">
-      <c r="B372" s="2"/>
-    </row>
-    <row r="373" spans="2:2">
-      <c r="B373" s="2"/>
+    <row r="364" spans="2:2">
+      <c r="B364" s="2"/>
+    </row>
+    <row r="365" spans="2:2">
+      <c r="B365" s="2"/>
     </row>
     <row r="374" spans="2:2">
       <c r="B374" s="2"/>
@@ -1451,62 +1545,74 @@
     <row r="375" spans="2:2">
       <c r="B375" s="2"/>
     </row>
-    <row r="380" spans="2:2">
-      <c r="B380" s="7"/>
-    </row>
-    <row r="410" spans="2:2">
-      <c r="B410" s="2"/>
-    </row>
-    <row r="411" spans="2:2">
-      <c r="B411" s="2"/>
-    </row>
-    <row r="412" spans="2:2">
-      <c r="B412" s="2"/>
-    </row>
-    <row r="413" spans="2:2">
-      <c r="B413" s="2"/>
-    </row>
-    <row r="438" spans="2:2">
-      <c r="B438" s="4"/>
-    </row>
-    <row r="439" spans="2:2">
-      <c r="B439" s="2"/>
-    </row>
-    <row r="440" spans="2:2">
-      <c r="B440" s="2"/>
-    </row>
-    <row r="441" spans="2:2">
-      <c r="B441" s="2"/>
-    </row>
-    <row r="473" spans="2:2">
-      <c r="B473" s="2"/>
-    </row>
-    <row r="474" spans="2:2">
-      <c r="B474" s="2"/>
-    </row>
-    <row r="475" spans="2:2">
-      <c r="B475" s="2"/>
-    </row>
-    <row r="476" spans="2:2">
-      <c r="B476" s="2"/>
-    </row>
-    <row r="477" spans="2:2">
-      <c r="B477" s="2"/>
-    </row>
-    <row r="479" spans="2:2">
-      <c r="B479" s="2"/>
-    </row>
-    <row r="482" spans="2:2">
-      <c r="B482" s="2"/>
-    </row>
-    <row r="483" spans="2:2">
-      <c r="B483" s="2"/>
-    </row>
-    <row r="484" spans="2:2">
-      <c r="B484" s="2"/>
-    </row>
-    <row r="485" spans="2:2">
-      <c r="B485" s="2"/>
+    <row r="376" spans="2:2">
+      <c r="B376" s="2"/>
+    </row>
+    <row r="377" spans="2:2">
+      <c r="B377" s="2"/>
+    </row>
+    <row r="390" spans="2:2">
+      <c r="B390" s="2"/>
+    </row>
+    <row r="391" spans="2:2">
+      <c r="B391" s="2"/>
+    </row>
+    <row r="392" spans="2:2">
+      <c r="B392" s="2"/>
+    </row>
+    <row r="393" spans="2:2">
+      <c r="B393" s="2"/>
+    </row>
+    <row r="398" spans="2:2">
+      <c r="B398" s="7"/>
+    </row>
+    <row r="428" spans="2:2">
+      <c r="B428" s="2"/>
+    </row>
+    <row r="429" spans="2:2">
+      <c r="B429" s="2"/>
+    </row>
+    <row r="430" spans="2:2">
+      <c r="B430" s="2"/>
+    </row>
+    <row r="431" spans="2:2">
+      <c r="B431" s="2"/>
+    </row>
+    <row r="456" spans="2:2">
+      <c r="B456" s="4"/>
+    </row>
+    <row r="457" spans="2:2">
+      <c r="B457" s="2"/>
+    </row>
+    <row r="458" spans="2:2">
+      <c r="B458" s="2"/>
+    </row>
+    <row r="459" spans="2:2">
+      <c r="B459" s="2"/>
+    </row>
+    <row r="491" spans="2:2">
+      <c r="B491" s="2"/>
+    </row>
+    <row r="492" spans="2:2">
+      <c r="B492" s="2"/>
+    </row>
+    <row r="493" spans="2:2">
+      <c r="B493" s="2"/>
+    </row>
+    <row r="494" spans="2:2">
+      <c r="B494" s="2"/>
+    </row>
+    <row r="495" spans="2:2">
+      <c r="B495" s="2"/>
+    </row>
+    <row r="497" spans="2:2">
+      <c r="B497" s="2"/>
+    </row>
+    <row r="500" spans="2:2">
+      <c r="B500" s="2"/>
+    </row>
+    <row r="501" spans="2:2">
+      <c r="B501" s="2"/>
     </row>
     <row r="502" spans="2:2">
       <c r="B502" s="2"/>
@@ -1514,12 +1620,6 @@
     <row r="503" spans="2:2">
       <c r="B503" s="2"/>
     </row>
-    <row r="504" spans="2:2">
-      <c r="B504" s="2"/>
-    </row>
-    <row r="519" spans="2:2">
-      <c r="B519" s="4"/>
-    </row>
     <row r="520" spans="2:2">
       <c r="B520" s="2"/>
     </row>
@@ -1529,11 +1629,8 @@
     <row r="522" spans="2:2">
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="2:2">
-      <c r="B523" s="2"/>
-    </row>
-    <row r="532" spans="2:2">
-      <c r="B532" s="2"/>
+    <row r="537" spans="2:2">
+      <c r="B537" s="4"/>
     </row>
     <row r="538" spans="2:2">
       <c r="B538" s="2"/>
@@ -1541,14 +1638,29 @@
     <row r="539" spans="2:2">
       <c r="B539" s="2"/>
     </row>
+    <row r="540" spans="2:2">
+      <c r="B540" s="2"/>
+    </row>
     <row r="541" spans="2:2">
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="2:2">
-      <c r="B542" s="2"/>
-    </row>
     <row r="550" spans="2:2">
       <c r="B550" s="2"/>
+    </row>
+    <row r="556" spans="2:2">
+      <c r="B556" s="2"/>
+    </row>
+    <row r="557" spans="2:2">
+      <c r="B557" s="2"/>
+    </row>
+    <row r="559" spans="2:2">
+      <c r="B559" s="2"/>
+    </row>
+    <row r="560" spans="2:2">
+      <c r="B560" s="2"/>
+    </row>
+    <row r="568" spans="2:2">
+      <c r="B568" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/shixun/李宗效工作日报.xlsx
+++ b/shixun/李宗效工作日报.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15720" windowHeight="11090"/>
+    <workbookView windowWidth="25600" windowHeight="11190"/>
   </bookViews>
   <sheets>
     <sheet name="12月" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+  <si>
+    <t>当日小结（12.22）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习</t>
+  </si>
+  <si>
+    <t>2、2道leetcode</t>
+  </si>
+  <si>
+    <t>3、复习C++</t>
+  </si>
+  <si>
+    <t>当日小结（12.21）</t>
+  </si>
+  <si>
+    <t>1、完成实践一ppt</t>
+  </si>
+  <si>
+    <t>3、复习C++(80%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.20）</t>
+  </si>
+  <si>
+    <t>1、完成c++缺陷检测</t>
+  </si>
+  <si>
+    <t>3、复习C++(60%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.19）</t>
+  </si>
+  <si>
+    <t>1、完成cmake构建编译opencv任务</t>
+  </si>
+  <si>
+    <t>当日小结（12.18）</t>
+  </si>
+  <si>
+    <t>1、完成ImageWatch，c++的opencv操作任务</t>
+  </si>
+  <si>
+    <t>3、复习C++(40%)</t>
+  </si>
+  <si>
+    <t>当日小结（12.17）</t>
+  </si>
+  <si>
+    <t>1、完成QT，MFC任务</t>
+  </si>
   <si>
     <t>当日小结（12.16）</t>
   </si>
@@ -1094,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:E568"/>
+  <dimension ref="B1:E602"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="73.9636363636364" customWidth="1"/>
@@ -1116,7 +1167,7 @@
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1132,209 +1183,285 @@
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="2" t="s">
-        <v>15</v>
+      <c r="B24" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="1" t="s">
+    <row r="32" spans="2:2">
+      <c r="B32" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="2" t="s">
+    <row r="36" spans="2:2">
+      <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="2" t="s">
+    <row r="37" spans="2:2">
+      <c r="B37" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="1" t="s">
+    <row r="38" spans="2:2">
+      <c r="B38" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="2" t="s">
+    <row r="41" spans="2:2">
+      <c r="B41" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="2" t="s">
+    <row r="42" spans="2:2">
+      <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="2"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="1" t="s">
+    <row r="43" spans="2:2">
+      <c r="B43" s="2" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="2" t="s">
+    <row r="52" spans="2:2">
+      <c r="B52" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="2"/>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="1" t="s">
+    <row r="53" spans="2:2">
+      <c r="B53" s="2" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="49" ht="28" spans="2:2">
-      <c r="B49" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" s="1"/>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="2" t="s">
+    <row r="62" spans="2:2">
+      <c r="B62" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="2"/>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="2"/>
-    </row>
     <row r="63" spans="2:2">
-      <c r="B63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="2"/>
     </row>
-    <row r="71" spans="2:2">
-      <c r="B71" s="2"/>
-    </row>
-    <row r="91" spans="2:3">
+    <row r="72" spans="2:2">
+      <c r="B72" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="2"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" ht="28" spans="2:2">
+      <c r="B83" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="1"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="2"/>
+    </row>
+    <row r="91" spans="2:2">
       <c r="B91" s="2"/>
     </row>
-    <row r="92" spans="2:3">
-      <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
-    </row>
-    <row r="93" spans="2:3">
-      <c r="B93" s="2"/>
-    </row>
-    <row r="94" spans="2:3">
-      <c r="B94" s="2"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="2"/>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="2"/>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="2"/>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="4"/>
+    <row r="95" spans="2:2">
+      <c r="B95" s="2"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="2"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="2"/>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" s="2"/>
@@ -1342,59 +1469,72 @@
     <row r="104" spans="2:2">
       <c r="B104" s="2"/>
     </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="2"/>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="2"/>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="2"/>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="2"/>
-    </row>
-    <row r="146" spans="2:2">
-      <c r="B146" s="2"/>
-    </row>
-    <row r="147" spans="2:2">
-      <c r="B147" s="2"/>
-    </row>
-    <row r="148" spans="2:2">
-      <c r="B148" s="2"/>
-    </row>
-    <row r="166" spans="2:2">
-      <c r="B166" s="2"/>
-    </row>
-    <row r="171" spans="2:2">
-      <c r="B171" s="2"/>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="2"/>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="2"/>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="2"/>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="2"/>
-    </row>
-    <row r="220" spans="2:2">
-      <c r="B220" s="2"/>
-    </row>
-    <row r="221" spans="2:2">
-      <c r="B221" s="2"/>
-    </row>
-    <row r="227" spans="2:2">
-      <c r="B227" s="2"/>
-    </row>
-    <row r="228" spans="2:2">
-      <c r="B228" s="2"/>
+    <row r="105" spans="2:2">
+      <c r="B105" s="2"/>
+    </row>
+    <row r="125" spans="2:3">
+      <c r="B125" s="2"/>
+    </row>
+    <row r="126" spans="2:3">
+      <c r="B126" s="2"/>
+      <c r="C126" s="3"/>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="B127" s="2"/>
+    </row>
+    <row r="128" spans="2:3">
+      <c r="B128" s="2"/>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133" s="2"/>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134" s="2"/>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" s="2"/>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" s="4"/>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="2"/>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" s="2"/>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" s="2"/>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="2"/>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" s="2"/>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" s="2"/>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" s="2"/>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" s="2"/>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" s="2"/>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" s="2"/>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" s="2"/>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="2"/>
     </row>
     <row r="229" spans="2:2">
-      <c r="B229" s="5"/>
+      <c r="B229" s="2"/>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" s="2"/>
@@ -1402,35 +1542,20 @@
     <row r="231" spans="2:2">
       <c r="B231" s="2"/>
     </row>
-    <row r="239" spans="2:2">
-      <c r="B239" s="2"/>
-    </row>
-    <row r="240" spans="2:2">
-      <c r="B240" s="2"/>
-    </row>
-    <row r="241" spans="2:2">
-      <c r="B241" s="2"/>
-    </row>
-    <row r="242" spans="2:2">
-      <c r="B242" s="2"/>
-    </row>
-    <row r="243" spans="2:2">
-      <c r="B243" s="2"/>
+    <row r="254" spans="2:2">
+      <c r="B254" s="2"/>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" s="2"/>
     </row>
-    <row r="256" spans="2:2">
-      <c r="B256" s="2"/>
-    </row>
-    <row r="257" spans="2:2">
-      <c r="B257" s="2"/>
-    </row>
-    <row r="258" spans="2:2">
-      <c r="B258" s="2"/>
-    </row>
-    <row r="259" spans="2:2">
-      <c r="B259" s="2"/>
+    <row r="261" spans="2:2">
+      <c r="B261" s="2"/>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262" s="2"/>
+    </row>
+    <row r="263" spans="2:2">
+      <c r="B263" s="5"/>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" s="2"/>
@@ -1438,11 +1563,11 @@
     <row r="265" spans="2:2">
       <c r="B265" s="2"/>
     </row>
-    <row r="266" spans="2:2">
-      <c r="B266" s="2"/>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" s="2"/>
+    <row r="273" spans="2:2">
+      <c r="B273" s="2"/>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" s="2"/>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" s="2"/>
@@ -1450,43 +1575,41 @@
     <row r="276" spans="2:2">
       <c r="B276" s="2"/>
     </row>
-    <row r="281" spans="2:2">
-      <c r="B281" s="2"/>
-    </row>
-    <row r="282" spans="2:2">
-      <c r="B282" s="2"/>
-    </row>
-    <row r="283" spans="2:2">
-      <c r="B283" s="2"/>
-    </row>
-    <row r="290" spans="2:5">
+    <row r="277" spans="2:2">
+      <c r="B277" s="2"/>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" s="2"/>
+    </row>
+    <row r="290" spans="2:2">
       <c r="B290" s="2"/>
     </row>
-    <row r="295" spans="2:5">
-      <c r="B295" s="2"/>
-    </row>
-    <row r="296" spans="2:5">
-      <c r="B296" s="2"/>
-      <c r="E296" s="1"/>
-    </row>
-    <row r="297" spans="2:5">
-      <c r="B297" s="2"/>
-      <c r="E297" s="1"/>
-    </row>
-    <row r="303" spans="2:5">
-      <c r="B303" s="2"/>
-    </row>
-    <row r="304" spans="2:5">
-      <c r="B304" s="2"/>
-    </row>
-    <row r="305" spans="2:2">
-      <c r="B305" s="4"/>
-    </row>
-    <row r="306" spans="2:2">
-      <c r="B306" s="2"/>
-    </row>
-    <row r="307" spans="2:2">
-      <c r="B307" s="6"/>
+    <row r="291" spans="2:2">
+      <c r="B291" s="2"/>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" s="2"/>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" s="2"/>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="2"/>
+    </row>
+    <row r="299" spans="2:2">
+      <c r="B299" s="2"/>
+    </row>
+    <row r="300" spans="2:2">
+      <c r="B300" s="2"/>
+    </row>
+    <row r="301" spans="2:2">
+      <c r="B301" s="2"/>
+    </row>
+    <row r="309" spans="2:2">
+      <c r="B309" s="2"/>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" s="2"/>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" s="2"/>
@@ -1497,98 +1620,127 @@
     <row r="317" spans="2:2">
       <c r="B317" s="2"/>
     </row>
-    <row r="318" spans="2:2">
-      <c r="B318" s="2"/>
-    </row>
-    <row r="319" spans="2:2">
-      <c r="B319" s="2"/>
-    </row>
-    <row r="320" spans="2:2">
-      <c r="B320" s="2"/>
-    </row>
-    <row r="322" spans="2:2">
-      <c r="B322" s="2"/>
-    </row>
-    <row r="325" spans="2:2">
-      <c r="B325" s="2"/>
-    </row>
-    <row r="335" spans="2:2">
-      <c r="B335" s="2"/>
-    </row>
-    <row r="336" spans="2:2">
-      <c r="B336" s="2"/>
+    <row r="324" spans="2:5">
+      <c r="B324" s="2"/>
+    </row>
+    <row r="329" spans="2:5">
+      <c r="B329" s="2"/>
+    </row>
+    <row r="330" spans="2:5">
+      <c r="B330" s="2"/>
+      <c r="E330" s="1"/>
+    </row>
+    <row r="331" spans="2:5">
+      <c r="B331" s="2"/>
+      <c r="E331" s="1"/>
     </row>
     <row r="337" spans="2:2">
-      <c r="B337" s="4"/>
+      <c r="B337" s="2"/>
     </row>
     <row r="338" spans="2:2">
       <c r="B338" s="2"/>
     </row>
     <row r="339" spans="2:2">
-      <c r="B339" s="2"/>
-    </row>
-    <row r="345" spans="2:2">
-      <c r="B345" s="2"/>
-    </row>
-    <row r="346" spans="2:2">
-      <c r="B346" s="2"/>
-    </row>
-    <row r="364" spans="2:2">
-      <c r="B364" s="2"/>
-    </row>
-    <row r="365" spans="2:2">
-      <c r="B365" s="2"/>
-    </row>
-    <row r="374" spans="2:2">
-      <c r="B374" s="2"/>
-    </row>
-    <row r="375" spans="2:2">
-      <c r="B375" s="2"/>
-    </row>
-    <row r="376" spans="2:2">
-      <c r="B376" s="2"/>
-    </row>
-    <row r="377" spans="2:2">
-      <c r="B377" s="2"/>
-    </row>
-    <row r="390" spans="2:2">
-      <c r="B390" s="2"/>
-    </row>
-    <row r="391" spans="2:2">
-      <c r="B391" s="2"/>
-    </row>
-    <row r="392" spans="2:2">
-      <c r="B392" s="2"/>
-    </row>
-    <row r="393" spans="2:2">
-      <c r="B393" s="2"/>
+      <c r="B339" s="4"/>
+    </row>
+    <row r="340" spans="2:2">
+      <c r="B340" s="2"/>
+    </row>
+    <row r="341" spans="2:2">
+      <c r="B341" s="6"/>
+    </row>
+    <row r="349" spans="2:2">
+      <c r="B349" s="2"/>
+    </row>
+    <row r="350" spans="2:2">
+      <c r="B350" s="2"/>
+    </row>
+    <row r="351" spans="2:2">
+      <c r="B351" s="2"/>
+    </row>
+    <row r="352" spans="2:2">
+      <c r="B352" s="2"/>
+    </row>
+    <row r="353" spans="2:2">
+      <c r="B353" s="2"/>
+    </row>
+    <row r="354" spans="2:2">
+      <c r="B354" s="2"/>
+    </row>
+    <row r="356" spans="2:2">
+      <c r="B356" s="2"/>
+    </row>
+    <row r="359" spans="2:2">
+      <c r="B359" s="2"/>
+    </row>
+    <row r="369" spans="2:2">
+      <c r="B369" s="2"/>
+    </row>
+    <row r="370" spans="2:2">
+      <c r="B370" s="2"/>
+    </row>
+    <row r="371" spans="2:2">
+      <c r="B371" s="4"/>
+    </row>
+    <row r="372" spans="2:2">
+      <c r="B372" s="2"/>
+    </row>
+    <row r="373" spans="2:2">
+      <c r="B373" s="2"/>
+    </row>
+    <row r="379" spans="2:2">
+      <c r="B379" s="2"/>
+    </row>
+    <row r="380" spans="2:2">
+      <c r="B380" s="2"/>
     </row>
     <row r="398" spans="2:2">
-      <c r="B398" s="7"/>
-    </row>
-    <row r="428" spans="2:2">
-      <c r="B428" s="2"/>
-    </row>
-    <row r="429" spans="2:2">
-      <c r="B429" s="2"/>
-    </row>
-    <row r="430" spans="2:2">
-      <c r="B430" s="2"/>
-    </row>
-    <row r="431" spans="2:2">
-      <c r="B431" s="2"/>
-    </row>
-    <row r="456" spans="2:2">
-      <c r="B456" s="4"/>
-    </row>
-    <row r="457" spans="2:2">
-      <c r="B457" s="2"/>
-    </row>
-    <row r="458" spans="2:2">
-      <c r="B458" s="2"/>
-    </row>
-    <row r="459" spans="2:2">
-      <c r="B459" s="2"/>
+      <c r="B398" s="2"/>
+    </row>
+    <row r="399" spans="2:2">
+      <c r="B399" s="2"/>
+    </row>
+    <row r="408" spans="2:2">
+      <c r="B408" s="2"/>
+    </row>
+    <row r="409" spans="2:2">
+      <c r="B409" s="2"/>
+    </row>
+    <row r="410" spans="2:2">
+      <c r="B410" s="2"/>
+    </row>
+    <row r="411" spans="2:2">
+      <c r="B411" s="2"/>
+    </row>
+    <row r="424" spans="2:2">
+      <c r="B424" s="2"/>
+    </row>
+    <row r="425" spans="2:2">
+      <c r="B425" s="2"/>
+    </row>
+    <row r="426" spans="2:2">
+      <c r="B426" s="2"/>
+    </row>
+    <row r="427" spans="2:2">
+      <c r="B427" s="2"/>
+    </row>
+    <row r="432" spans="2:2">
+      <c r="B432" s="7"/>
+    </row>
+    <row r="462" spans="2:2">
+      <c r="B462" s="2"/>
+    </row>
+    <row r="463" spans="2:2">
+      <c r="B463" s="2"/>
+    </row>
+    <row r="464" spans="2:2">
+      <c r="B464" s="2"/>
+    </row>
+    <row r="465" spans="2:2">
+      <c r="B465" s="2"/>
+    </row>
+    <row r="490" spans="2:2">
+      <c r="B490" s="4"/>
     </row>
     <row r="491" spans="2:2">
       <c r="B491" s="2"/>
@@ -1599,68 +1751,77 @@
     <row r="493" spans="2:2">
       <c r="B493" s="2"/>
     </row>
-    <row r="494" spans="2:2">
-      <c r="B494" s="2"/>
-    </row>
-    <row r="495" spans="2:2">
-      <c r="B495" s="2"/>
-    </row>
-    <row r="497" spans="2:2">
-      <c r="B497" s="2"/>
-    </row>
-    <row r="500" spans="2:2">
-      <c r="B500" s="2"/>
-    </row>
-    <row r="501" spans="2:2">
-      <c r="B501" s="2"/>
-    </row>
-    <row r="502" spans="2:2">
-      <c r="B502" s="2"/>
-    </row>
-    <row r="503" spans="2:2">
-      <c r="B503" s="2"/>
-    </row>
-    <row r="520" spans="2:2">
-      <c r="B520" s="2"/>
-    </row>
-    <row r="521" spans="2:2">
-      <c r="B521" s="2"/>
-    </row>
-    <row r="522" spans="2:2">
-      <c r="B522" s="2"/>
+    <row r="525" spans="2:2">
+      <c r="B525" s="2"/>
+    </row>
+    <row r="526" spans="2:2">
+      <c r="B526" s="2"/>
+    </row>
+    <row r="527" spans="2:2">
+      <c r="B527" s="2"/>
+    </row>
+    <row r="528" spans="2:2">
+      <c r="B528" s="2"/>
+    </row>
+    <row r="529" spans="2:2">
+      <c r="B529" s="2"/>
+    </row>
+    <row r="531" spans="2:2">
+      <c r="B531" s="2"/>
+    </row>
+    <row r="534" spans="2:2">
+      <c r="B534" s="2"/>
+    </row>
+    <row r="535" spans="2:2">
+      <c r="B535" s="2"/>
+    </row>
+    <row r="536" spans="2:2">
+      <c r="B536" s="2"/>
     </row>
     <row r="537" spans="2:2">
-      <c r="B537" s="4"/>
-    </row>
-    <row r="538" spans="2:2">
-      <c r="B538" s="2"/>
-    </row>
-    <row r="539" spans="2:2">
-      <c r="B539" s="2"/>
-    </row>
-    <row r="540" spans="2:2">
-      <c r="B540" s="2"/>
-    </row>
-    <row r="541" spans="2:2">
-      <c r="B541" s="2"/>
-    </row>
-    <row r="550" spans="2:2">
-      <c r="B550" s="2"/>
+      <c r="B537" s="2"/>
+    </row>
+    <row r="554" spans="2:2">
+      <c r="B554" s="2"/>
+    </row>
+    <row r="555" spans="2:2">
+      <c r="B555" s="2"/>
     </row>
     <row r="556" spans="2:2">
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="2:2">
-      <c r="B557" s="2"/>
-    </row>
-    <row r="559" spans="2:2">
-      <c r="B559" s="2"/>
-    </row>
-    <row r="560" spans="2:2">
-      <c r="B560" s="2"/>
-    </row>
-    <row r="568" spans="2:2">
-      <c r="B568" s="2"/>
+    <row r="571" spans="2:2">
+      <c r="B571" s="4"/>
+    </row>
+    <row r="572" spans="2:2">
+      <c r="B572" s="2"/>
+    </row>
+    <row r="573" spans="2:2">
+      <c r="B573" s="2"/>
+    </row>
+    <row r="574" spans="2:2">
+      <c r="B574" s="2"/>
+    </row>
+    <row r="575" spans="2:2">
+      <c r="B575" s="2"/>
+    </row>
+    <row r="584" spans="2:2">
+      <c r="B584" s="2"/>
+    </row>
+    <row r="590" spans="2:2">
+      <c r="B590" s="2"/>
+    </row>
+    <row r="591" spans="2:2">
+      <c r="B591" s="2"/>
+    </row>
+    <row r="593" spans="2:2">
+      <c r="B593" s="2"/>
+    </row>
+    <row r="594" spans="2:2">
+      <c r="B594" s="2"/>
+    </row>
+    <row r="602" spans="2:2">
+      <c r="B602" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/shixun/李宗效工作日报.xlsx
+++ b/shixun/李宗效工作日报.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11190"/>
+    <workbookView windowWidth="25600" windowHeight="11190" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="12月" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+  <si>
+    <t>当日小结（12.30）</t>
+  </si>
+  <si>
+    <t>1、完成大模型(80%)</t>
+  </si>
+  <si>
+    <t>2、2道leetcode</t>
+  </si>
+  <si>
+    <t>1、完成猫狗识别，车辆检测</t>
+  </si>
+  <si>
+    <t>当日小结（12.29）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(42/158)</t>
+  </si>
+  <si>
+    <t>当日小结（12.28）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(37/158)</t>
+  </si>
+  <si>
+    <t>当日小结（12.27）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(32/158)</t>
+  </si>
+  <si>
+    <t>当日小结（12.26）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(27/158)</t>
+  </si>
+  <si>
+    <t>当日小结（12.25）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(22/158)</t>
+  </si>
+  <si>
+    <t>3、完成手写识别</t>
+  </si>
+  <si>
+    <t>当日小结（12.24）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(16/158)</t>
+  </si>
+  <si>
+    <t>当日小结（12.23）</t>
+  </si>
+  <si>
+    <t>1、复习深度学习(10/158)</t>
+  </si>
   <si>
     <t>当日小结（12.22）</t>
   </si>
   <si>
-    <t>1、复习深度学习</t>
-  </si>
-  <si>
-    <t>2、2道leetcode</t>
+    <t>1、复习深度学习(5/158)</t>
   </si>
   <si>
     <t>3、复习C++</t>
@@ -186,6 +240,18 @@
   </si>
   <si>
     <t>2、完成opencv练习的前4章</t>
+  </si>
+  <si>
+    <t>当日小结（01.05）</t>
+  </si>
+  <si>
+    <t>1、完成实践2</t>
+  </si>
+  <si>
+    <t>当日小结（01.01）</t>
+  </si>
+  <si>
+    <t>1、完成大模型</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:E602"/>
+  <dimension ref="B1:E648"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="73.9636363636364" customWidth="1"/>
@@ -1166,354 +1232,470 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
+    <row r="6" spans="2:2">
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="2" t="s">
+    <row r="13" spans="2:2">
+      <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
-      <c r="B10" t="s">
+    <row r="16" spans="2:2">
+      <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="1" t="s">
+    <row r="17" spans="2:2">
+      <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="2" t="s">
+    <row r="18" spans="2:2">
+      <c r="B18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="2" t="s">
+    <row r="22" spans="2:2">
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="1" t="s">
+    <row r="24" spans="2:2">
+      <c r="B24" s="2"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="2" t="s">
+    <row r="27" spans="2:2">
+      <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="2" t="s">
+    <row r="28" spans="2:2">
+      <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="1" t="s">
+    <row r="31" spans="2:2">
+      <c r="B31" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="2" t="s">
-        <v>18</v>
+    <row r="34" spans="2:2">
+      <c r="B34" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="2" t="s">
-        <v>19</v>
+      <c r="B37" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="2:2">
-      <c r="B42" s="2" t="s">
-        <v>22</v>
+      <c r="B42" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="1" t="s">
-        <v>28</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="2:2">
-      <c r="B53" s="2" t="s">
-        <v>29</v>
+      <c r="B53" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="1" t="s">
+    <row r="71" spans="2:2">
+      <c r="B71" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="2" t="s">
+    <row r="72" spans="2:2">
+      <c r="B72" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="2" t="s">
+    <row r="76" spans="2:2">
+      <c r="B76" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="1" t="s">
+    <row r="77" spans="2:2">
+      <c r="B77" s="2" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2">
-      <c r="B68" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="2"/>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" ht="28" spans="2:2">
+      <c r="B82" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
       <c r="B83" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="1"/>
-    </row>
-    <row r="86" spans="2:2">
-      <c r="B86" s="1"/>
+        <v>38</v>
+      </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="2"/>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91" s="2"/>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95" s="2"/>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="2"/>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="2"/>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" s="2"/>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" s="2"/>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="2"/>
-    </row>
-    <row r="125" spans="2:3">
-      <c r="B125" s="2"/>
-    </row>
-    <row r="126" spans="2:3">
+    <row r="108" spans="2:2">
+      <c r="B108" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="2"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
       <c r="B126" s="2"/>
-      <c r="C126" s="3"/>
-    </row>
-    <row r="127" spans="2:3">
-      <c r="B127" s="2"/>
-    </row>
-    <row r="128" spans="2:3">
-      <c r="B128" s="2"/>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="129" ht="28" spans="2:2">
+      <c r="B129" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" s="1"/>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132" s="1"/>
     </row>
     <row r="133" spans="2:2">
-      <c r="B133" s="2"/>
+      <c r="B133" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="134" spans="2:2">
-      <c r="B134" s="2"/>
+      <c r="B134" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="135" spans="2:2">
-      <c r="B135" s="2"/>
+      <c r="B135" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="136" spans="2:2">
-      <c r="B136" s="4"/>
+      <c r="B136" s="2"/>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" s="2"/>
     </row>
-    <row r="138" spans="2:2">
-      <c r="B138" s="2"/>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="2"/>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="2"/>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" s="2"/>
-    </row>
-    <row r="158" spans="2:2">
-      <c r="B158" s="2"/>
+    <row r="141" spans="2:2">
+      <c r="B141" s="2"/>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" s="2"/>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="2"/>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="2"/>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150" s="2"/>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" s="2"/>
+    </row>
+    <row r="171" spans="2:3">
+      <c r="B171" s="2"/>
+    </row>
+    <row r="172" spans="2:3">
+      <c r="B172" s="2"/>
+      <c r="C172" s="3"/>
+    </row>
+    <row r="173" spans="2:3">
+      <c r="B173" s="2"/>
+    </row>
+    <row r="174" spans="2:3">
+      <c r="B174" s="2"/>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="2"/>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" s="2"/>
@@ -1522,52 +1704,43 @@
       <c r="B181" s="2"/>
     </row>
     <row r="182" spans="2:2">
-      <c r="B182" s="2"/>
+      <c r="B182" s="4"/>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" s="2"/>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" s="2"/>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" s="2"/>
     </row>
     <row r="200" spans="2:2">
       <c r="B200" s="2"/>
     </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="2"/>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="2"/>
-    </row>
-    <row r="229" spans="2:2">
-      <c r="B229" s="2"/>
-    </row>
-    <row r="230" spans="2:2">
-      <c r="B230" s="2"/>
-    </row>
-    <row r="231" spans="2:2">
-      <c r="B231" s="2"/>
-    </row>
-    <row r="254" spans="2:2">
-      <c r="B254" s="2"/>
-    </row>
-    <row r="255" spans="2:2">
-      <c r="B255" s="2"/>
-    </row>
-    <row r="261" spans="2:2">
-      <c r="B261" s="2"/>
-    </row>
-    <row r="262" spans="2:2">
-      <c r="B262" s="2"/>
-    </row>
-    <row r="263" spans="2:2">
-      <c r="B263" s="5"/>
-    </row>
-    <row r="264" spans="2:2">
-      <c r="B264" s="2"/>
-    </row>
-    <row r="265" spans="2:2">
-      <c r="B265" s="2"/>
-    </row>
-    <row r="273" spans="2:2">
-      <c r="B273" s="2"/>
-    </row>
-    <row r="274" spans="2:2">
-      <c r="B274" s="2"/>
+    <row r="203" spans="2:2">
+      <c r="B203" s="2"/>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" s="2"/>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" s="2"/>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" s="2"/>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" s="2"/>
+    </row>
+    <row r="246" spans="2:2">
+      <c r="B246" s="2"/>
+    </row>
+    <row r="251" spans="2:2">
+      <c r="B251" s="2"/>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="2"/>
     </row>
     <row r="275" spans="2:2">
       <c r="B275" s="2"/>
@@ -1578,61 +1751,47 @@
     <row r="277" spans="2:2">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="2:2">
-      <c r="B289" s="2"/>
-    </row>
-    <row r="290" spans="2:2">
-      <c r="B290" s="2"/>
-    </row>
-    <row r="291" spans="2:2">
-      <c r="B291" s="2"/>
-    </row>
-    <row r="292" spans="2:2">
-      <c r="B292" s="2"/>
-    </row>
-    <row r="293" spans="2:2">
-      <c r="B293" s="2"/>
-    </row>
-    <row r="298" spans="2:2">
-      <c r="B298" s="2"/>
-    </row>
-    <row r="299" spans="2:2">
-      <c r="B299" s="2"/>
-    </row>
     <row r="300" spans="2:2">
       <c r="B300" s="2"/>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" s="2"/>
     </row>
+    <row r="307" spans="2:2">
+      <c r="B307" s="2"/>
+    </row>
+    <row r="308" spans="2:2">
+      <c r="B308" s="2"/>
+    </row>
     <row r="309" spans="2:2">
-      <c r="B309" s="2"/>
+      <c r="B309" s="5"/>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" s="2"/>
     </row>
-    <row r="315" spans="2:2">
-      <c r="B315" s="2"/>
-    </row>
-    <row r="316" spans="2:2">
-      <c r="B316" s="2"/>
-    </row>
-    <row r="317" spans="2:2">
-      <c r="B317" s="2"/>
-    </row>
-    <row r="324" spans="2:5">
-      <c r="B324" s="2"/>
-    </row>
-    <row r="329" spans="2:5">
-      <c r="B329" s="2"/>
-    </row>
-    <row r="330" spans="2:5">
-      <c r="B330" s="2"/>
-      <c r="E330" s="1"/>
-    </row>
-    <row r="331" spans="2:5">
-      <c r="B331" s="2"/>
-      <c r="E331" s="1"/>
+    <row r="311" spans="2:2">
+      <c r="B311" s="2"/>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" s="2"/>
+    </row>
+    <row r="320" spans="2:2">
+      <c r="B320" s="2"/>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" s="2"/>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322" s="2"/>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" s="2"/>
+    </row>
+    <row r="335" spans="2:2">
+      <c r="B335" s="2"/>
+    </row>
+    <row r="336" spans="2:2">
+      <c r="B336" s="2"/>
     </row>
     <row r="337" spans="2:2">
       <c r="B337" s="2"/>
@@ -1641,58 +1800,72 @@
       <c r="B338" s="2"/>
     </row>
     <row r="339" spans="2:2">
-      <c r="B339" s="4"/>
-    </row>
-    <row r="340" spans="2:2">
-      <c r="B340" s="2"/>
-    </row>
-    <row r="341" spans="2:2">
-      <c r="B341" s="6"/>
-    </row>
-    <row r="349" spans="2:2">
-      <c r="B349" s="2"/>
-    </row>
-    <row r="350" spans="2:2">
-      <c r="B350" s="2"/>
-    </row>
-    <row r="351" spans="2:2">
-      <c r="B351" s="2"/>
-    </row>
-    <row r="352" spans="2:2">
-      <c r="B352" s="2"/>
-    </row>
-    <row r="353" spans="2:2">
-      <c r="B353" s="2"/>
-    </row>
-    <row r="354" spans="2:2">
-      <c r="B354" s="2"/>
+      <c r="B339" s="2"/>
+    </row>
+    <row r="344" spans="2:2">
+      <c r="B344" s="2"/>
+    </row>
+    <row r="345" spans="2:2">
+      <c r="B345" s="2"/>
+    </row>
+    <row r="346" spans="2:2">
+      <c r="B346" s="2"/>
+    </row>
+    <row r="347" spans="2:2">
+      <c r="B347" s="2"/>
+    </row>
+    <row r="355" spans="2:2">
+      <c r="B355" s="2"/>
     </row>
     <row r="356" spans="2:2">
       <c r="B356" s="2"/>
     </row>
-    <row r="359" spans="2:2">
-      <c r="B359" s="2"/>
-    </row>
-    <row r="369" spans="2:2">
-      <c r="B369" s="2"/>
-    </row>
-    <row r="370" spans="2:2">
+    <row r="361" spans="2:2">
+      <c r="B361" s="2"/>
+    </row>
+    <row r="362" spans="2:2">
+      <c r="B362" s="2"/>
+    </row>
+    <row r="363" spans="2:2">
+      <c r="B363" s="2"/>
+    </row>
+    <row r="370" spans="2:5">
       <c r="B370" s="2"/>
     </row>
-    <row r="371" spans="2:2">
-      <c r="B371" s="4"/>
-    </row>
-    <row r="372" spans="2:2">
-      <c r="B372" s="2"/>
-    </row>
-    <row r="373" spans="2:2">
-      <c r="B373" s="2"/>
-    </row>
-    <row r="379" spans="2:2">
-      <c r="B379" s="2"/>
-    </row>
-    <row r="380" spans="2:2">
-      <c r="B380" s="2"/>
+    <row r="375" spans="2:5">
+      <c r="B375" s="2"/>
+    </row>
+    <row r="376" spans="2:5">
+      <c r="B376" s="2"/>
+      <c r="E376" s="1"/>
+    </row>
+    <row r="377" spans="2:5">
+      <c r="B377" s="2"/>
+      <c r="E377" s="1"/>
+    </row>
+    <row r="383" spans="2:5">
+      <c r="B383" s="2"/>
+    </row>
+    <row r="384" spans="2:5">
+      <c r="B384" s="2"/>
+    </row>
+    <row r="385" spans="2:2">
+      <c r="B385" s="4"/>
+    </row>
+    <row r="386" spans="2:2">
+      <c r="B386" s="2"/>
+    </row>
+    <row r="387" spans="2:2">
+      <c r="B387" s="6"/>
+    </row>
+    <row r="395" spans="2:2">
+      <c r="B395" s="2"/>
+    </row>
+    <row r="396" spans="2:2">
+      <c r="B396" s="2"/>
+    </row>
+    <row r="397" spans="2:2">
+      <c r="B397" s="2"/>
     </row>
     <row r="398" spans="2:2">
       <c r="B398" s="2"/>
@@ -1700,20 +1873,29 @@
     <row r="399" spans="2:2">
       <c r="B399" s="2"/>
     </row>
-    <row r="408" spans="2:2">
-      <c r="B408" s="2"/>
-    </row>
-    <row r="409" spans="2:2">
-      <c r="B409" s="2"/>
-    </row>
-    <row r="410" spans="2:2">
-      <c r="B410" s="2"/>
-    </row>
-    <row r="411" spans="2:2">
-      <c r="B411" s="2"/>
-    </row>
-    <row r="424" spans="2:2">
-      <c r="B424" s="2"/>
+    <row r="400" spans="2:2">
+      <c r="B400" s="2"/>
+    </row>
+    <row r="402" spans="2:2">
+      <c r="B402" s="2"/>
+    </row>
+    <row r="405" spans="2:2">
+      <c r="B405" s="2"/>
+    </row>
+    <row r="415" spans="2:2">
+      <c r="B415" s="2"/>
+    </row>
+    <row r="416" spans="2:2">
+      <c r="B416" s="2"/>
+    </row>
+    <row r="417" spans="2:2">
+      <c r="B417" s="4"/>
+    </row>
+    <row r="418" spans="2:2">
+      <c r="B418" s="2"/>
+    </row>
+    <row r="419" spans="2:2">
+      <c r="B419" s="2"/>
     </row>
     <row r="425" spans="2:2">
       <c r="B425" s="2"/>
@@ -1721,77 +1903,65 @@
     <row r="426" spans="2:2">
       <c r="B426" s="2"/>
     </row>
-    <row r="427" spans="2:2">
-      <c r="B427" s="2"/>
-    </row>
-    <row r="432" spans="2:2">
-      <c r="B432" s="7"/>
-    </row>
-    <row r="462" spans="2:2">
-      <c r="B462" s="2"/>
-    </row>
-    <row r="463" spans="2:2">
-      <c r="B463" s="2"/>
-    </row>
-    <row r="464" spans="2:2">
-      <c r="B464" s="2"/>
-    </row>
-    <row r="465" spans="2:2">
-      <c r="B465" s="2"/>
-    </row>
-    <row r="490" spans="2:2">
-      <c r="B490" s="4"/>
-    </row>
-    <row r="491" spans="2:2">
-      <c r="B491" s="2"/>
-    </row>
-    <row r="492" spans="2:2">
-      <c r="B492" s="2"/>
-    </row>
-    <row r="493" spans="2:2">
-      <c r="B493" s="2"/>
-    </row>
-    <row r="525" spans="2:2">
-      <c r="B525" s="2"/>
-    </row>
-    <row r="526" spans="2:2">
-      <c r="B526" s="2"/>
-    </row>
-    <row r="527" spans="2:2">
-      <c r="B527" s="2"/>
-    </row>
-    <row r="528" spans="2:2">
-      <c r="B528" s="2"/>
-    </row>
-    <row r="529" spans="2:2">
-      <c r="B529" s="2"/>
-    </row>
-    <row r="531" spans="2:2">
-      <c r="B531" s="2"/>
-    </row>
-    <row r="534" spans="2:2">
-      <c r="B534" s="2"/>
-    </row>
-    <row r="535" spans="2:2">
-      <c r="B535" s="2"/>
+    <row r="444" spans="2:2">
+      <c r="B444" s="2"/>
+    </row>
+    <row r="445" spans="2:2">
+      <c r="B445" s="2"/>
+    </row>
+    <row r="454" spans="2:2">
+      <c r="B454" s="2"/>
+    </row>
+    <row r="455" spans="2:2">
+      <c r="B455" s="2"/>
+    </row>
+    <row r="456" spans="2:2">
+      <c r="B456" s="2"/>
+    </row>
+    <row r="457" spans="2:2">
+      <c r="B457" s="2"/>
+    </row>
+    <row r="470" spans="2:2">
+      <c r="B470" s="2"/>
+    </row>
+    <row r="471" spans="2:2">
+      <c r="B471" s="2"/>
+    </row>
+    <row r="472" spans="2:2">
+      <c r="B472" s="2"/>
+    </row>
+    <row r="473" spans="2:2">
+      <c r="B473" s="2"/>
+    </row>
+    <row r="478" spans="2:2">
+      <c r="B478" s="7"/>
+    </row>
+    <row r="508" spans="2:2">
+      <c r="B508" s="2"/>
+    </row>
+    <row r="509" spans="2:2">
+      <c r="B509" s="2"/>
+    </row>
+    <row r="510" spans="2:2">
+      <c r="B510" s="2"/>
+    </row>
+    <row r="511" spans="2:2">
+      <c r="B511" s="2"/>
     </row>
     <row r="536" spans="2:2">
-      <c r="B536" s="2"/>
+      <c r="B536" s="4"/>
     </row>
     <row r="537" spans="2:2">
       <c r="B537" s="2"/>
     </row>
-    <row r="554" spans="2:2">
-      <c r="B554" s="2"/>
-    </row>
-    <row r="555" spans="2:2">
-      <c r="B555" s="2"/>
-    </row>
-    <row r="556" spans="2:2">
-      <c r="B556" s="2"/>
+    <row r="538" spans="2:2">
+      <c r="B538" s="2"/>
+    </row>
+    <row r="539" spans="2:2">
+      <c r="B539" s="2"/>
     </row>
     <row r="571" spans="2:2">
-      <c r="B571" s="4"/>
+      <c r="B571" s="2"/>
     </row>
     <row r="572" spans="2:2">
       <c r="B572" s="2"/>
@@ -1805,23 +1975,62 @@
     <row r="575" spans="2:2">
       <c r="B575" s="2"/>
     </row>
-    <row r="584" spans="2:2">
-      <c r="B584" s="2"/>
-    </row>
-    <row r="590" spans="2:2">
-      <c r="B590" s="2"/>
-    </row>
-    <row r="591" spans="2:2">
-      <c r="B591" s="2"/>
-    </row>
-    <row r="593" spans="2:2">
-      <c r="B593" s="2"/>
-    </row>
-    <row r="594" spans="2:2">
-      <c r="B594" s="2"/>
+    <row r="577" spans="2:2">
+      <c r="B577" s="2"/>
+    </row>
+    <row r="580" spans="2:2">
+      <c r="B580" s="2"/>
+    </row>
+    <row r="581" spans="2:2">
+      <c r="B581" s="2"/>
+    </row>
+    <row r="582" spans="2:2">
+      <c r="B582" s="2"/>
+    </row>
+    <row r="583" spans="2:2">
+      <c r="B583" s="2"/>
+    </row>
+    <row r="600" spans="2:2">
+      <c r="B600" s="2"/>
+    </row>
+    <row r="601" spans="2:2">
+      <c r="B601" s="2"/>
     </row>
     <row r="602" spans="2:2">
       <c r="B602" s="2"/>
+    </row>
+    <row r="617" spans="2:2">
+      <c r="B617" s="4"/>
+    </row>
+    <row r="618" spans="2:2">
+      <c r="B618" s="2"/>
+    </row>
+    <row r="619" spans="2:2">
+      <c r="B619" s="2"/>
+    </row>
+    <row r="620" spans="2:2">
+      <c r="B620" s="2"/>
+    </row>
+    <row r="621" spans="2:2">
+      <c r="B621" s="2"/>
+    </row>
+    <row r="630" spans="2:2">
+      <c r="B630" s="2"/>
+    </row>
+    <row r="636" spans="2:2">
+      <c r="B636" s="2"/>
+    </row>
+    <row r="637" spans="2:2">
+      <c r="B637" s="2"/>
+    </row>
+    <row r="639" spans="2:2">
+      <c r="B639" s="2"/>
+    </row>
+    <row r="640" spans="2:2">
+      <c r="B640" s="2"/>
+    </row>
+    <row r="648" spans="2:2">
+      <c r="B648" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1833,9 +2042,43 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="B1:B8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="29.7272727272727" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="2:2">
+      <c r="B2" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1" spans="2:2">
+      <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
